--- a/output/pdf_financials_xlsx/PRNC.xlsx
+++ b/output/pdf_financials_xlsx/PRNC.xlsx
@@ -1659,10 +1659,10 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.018804</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.129957</v>
       </c>
     </row>
     <row r="93">
@@ -2498,7 +2498,11 @@
           <t>Reserves (Note 7)</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E9" s="5" t="n">
         <v>0.018804</v>
       </c>

--- a/output/pdf_financials_xlsx/PRNC.xlsx
+++ b/output/pdf_financials_xlsx/PRNC.xlsx
@@ -877,10 +877,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.011613</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>3.185465</v>
       </c>
     </row>
     <row r="35">
@@ -903,10 +903,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.011613</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>3.185465</v>
       </c>
     </row>
     <row r="37">
@@ -1059,10 +1059,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.011613</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>3.285164</v>
+        <v>0.099699</v>
       </c>
     </row>
     <row r="49">
@@ -2308,7 +2308,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -2388,7 +2388,11 @@
           <t>Reclamation deposit (Note 6)</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/PRNC.xlsx
+++ b/output/pdf_financials_xlsx/PRNC.xlsx
@@ -2912,7 +2912,11 @@
           <t>Private placement</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>-</t>
